--- a/daily_matches/job_matches_2026-06-08.xlsx
+++ b/daily_matches/job_matches_2026-06-08.xlsx
@@ -468,165 +468,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Document Intelligence</t>
+          <t>Senior Systems Engineer, Storage - DGX Cloud</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, PySpark, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba121f12561f2dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d775986eb12cc77d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, PostgreSQL, Python</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb2062b0a9a4e543</t>
+          <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer - Agentic AI Platform</t>
+          <t>Senior Data Architect: Clinical Solutions (Local / Hybrid)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Vanderbilt University Medical Center</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, PostgreSQL, Python</t>
+          <t>RAG, Data Lake, Git, Databricks, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5046c7fb781aaca</t>
+          <t>https://www.indeed.com/viewjob?jk=becf596f4f6a2be5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, PostgreSQL, Python</t>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356b9ce29a2e23b8</t>
+          <t>https://www.indeed.com/viewjob?jk=760a0f80beabd595</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tmi Universal Sports</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>Glue, Athena, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637f19c4ed7da859</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b9e1941fe0d4ca</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-08.xlsx
+++ b/daily_matches/job_matches_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, Storage - DGX Cloud</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>MOEV Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, Keras, S3, EC2, Kinesis, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d775986eb12cc77d</t>
+          <t>https://www.indeed.com/viewjob?jk=33470d4830492356</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>Machine Learning Engineer, AI Solutions Hub (AISH)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb267d00866d172</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Architect: Clinical Solutions (Local / Hybrid)</t>
+          <t>Techno Functional Solutions Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vanderbilt University Medical Center</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Databricks, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becf596f4f6a2be5</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6462d7517c54df</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Data Solutions LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,497 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760a0f80beabd595</t>
+          <t>https://www.indeed.com/viewjob?jk=beeeb3fef606575e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Java Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Symplore Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3af98f3363aa097a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Engineering Services</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Invesco</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, S3, Athena, CI/CD, Jenkins, Git, Snowflake, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Wowza Media Systems</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Glue, Data Lake, Docker, Kubernetes, Terraform, MySQL, SQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Metronet</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Snowflake, Databricks, PySpark, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Data / AI Application Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DDN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, BigQuery, FastAPI, CI/CD, Terraform, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7e1bc636a26547f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Databricks, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ec915a33af5dd7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GE Appliances</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=748e79b14f34bfaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GE Appliances</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a955d965bfa4be1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Pinecone, Docker, Kubernetes, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Public Storage</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PyTorch, XGBoost, MLflow, Git, Python, SQL, R, Bayesian</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67509bd262e9da6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Azure Cloud Architect (Local to MS)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=103f1bec7bf3fcc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Value Engineer - Banking</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Glue, Athena, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b9e1941fe0d4ca</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f71db1b3585c5981</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Data Product APIs</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>USA TODAY Co.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=066029fc5aa3367e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-08.xlsx
+++ b/daily_matches/job_matches_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Artificial Intelligence - AI Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MOEV Inc.</t>
+          <t>Pellera Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, Keras, S3, EC2, Kinesis, Docker, Kubernetes</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33470d4830492356</t>
+          <t>https://www.indeed.com/viewjob?jk=138d05ce77ce23e4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, AI Solutions Hub (AISH)</t>
+          <t>Artificial Intelligence - AI Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Pellera Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb267d00866d172</t>
+          <t>https://www.indeed.com/viewjob?jk=cd744c3c8c547e36</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Techno Functional Solutions Architect</t>
+          <t>Senior Software Engineer, AI and ML Platforms</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Bio-Techne</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6462d7517c54df</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac5bcd650b00da</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Senior Data/ML Engineer (AWS)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Data Solutions LLC</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Generative AI, RAG, Prompt Engineering, S3, Glue, Athena, Synapse, Data Lake, Kinesis, Quicksight</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beeeb3fef606575e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Java Developer</t>
+          <t>Matterport - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Symplore Inc</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af98f3363aa097a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e45d608f8cb1f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer, Engineering Services</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, Athena, CI/CD, Jenkins, Git, Snowflake, Python, SQL</t>
+          <t>RAG, Synapse, Data Lake, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
+          <t>https://www.indeed.com/viewjob?jk=877524bbcd4e4f56</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wowza Media Systems</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Data Lake, Docker, Kubernetes, Terraform, MySQL, SQL</t>
+          <t>Redshift, Data Lake, Apache Airflow, CI/CD, Jenkins, Git, Snowflake, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
+          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Kubernetes / XNAT Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Metronet</t>
+          <t>XNAT Works Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Snowflake, Databricks, PySpark, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=86cc83af06965162</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data / AI Application Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, FastAPI, CI/CD, Terraform, BigQuery, Python, SQL, R</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1bc636a26547f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5d6144c747c0b0b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning Engineer III, Search Relevance</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Databricks, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Terraform, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec915a33af5dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=7806dc41ae3cce01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748e79b14f34bfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=e446599f1b1f5c54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a955d965bfa4be1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7deb8cb5e2c28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Pinecone, Docker, Kubernetes, Kafka, Python, R, Java, Scala</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+          <t>https://www.indeed.com/viewjob?jk=a329ecdc04bedbd8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, XGBoost, MLflow, Git, Python, SQL, R, Bayesian</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67509bd262e9da6f</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e8c12fc04e7cef</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect (Local to MS)</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103f1bec7bf3fcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=391d69d149a1d2a0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Value Engineer - Banking</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,77 +1021,217 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f71db1b3585c5981</t>
+          <t>https://www.indeed.com/viewjob?jk=75c5fb49d9153d67</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Data Product APIs</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USA TODAY Co.</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=066029fc5aa3367e</t>
+          <t>https://www.indeed.com/viewjob?jk=abdb996f66f95a39</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>CLOUD5TECH</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MLflow, FastAPI, Snowflake, Databricks, PySpark, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9667dae25862c0f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>THEMESOFT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14376e2563bff55d</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Data Science Software LLC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d96ad5f2dd3ad96</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Data Product APIs</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>USA TODAY Co.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ce51dbe0b401ef3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Data Product APIs</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>USA TODAY Co.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a46068ce48058b8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-08.xlsx
+++ b/daily_matches/job_matches_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence - AI Architect</t>
+          <t>Senior Data Engineer, Analytics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pellera Technologies</t>
+          <t>Lovevery</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Generative AI, RAG, Copilot, Redshift, BigQuery, CI/CD, GitHub Actions, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138d05ce77ce23e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Artificial Intelligence - AI Architect</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pellera Technologies</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Cortex, MLflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd744c3c8c547e36</t>
+          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI and ML Platforms</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac5bcd650b00da</t>
+          <t>https://www.indeed.com/viewjob?jk=56cb3c3570936f9a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data/ML Engineer (AWS)</t>
+          <t>Sr AI/ML Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, S3, Glue, Athena, Synapse, Data Lake, Kinesis, Quicksight</t>
+          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
+          <t>https://www.indeed.com/viewjob?jk=d66a41a341ceb596</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Matterport - Senior Software Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, FAISS, Pinecone, TensorFlow, PyTorch, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e45d608f8cb1f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b40c1bc8dda813c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior BI Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Soleo Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
+          <t>RAG, Synapse, Data Lake, Dataflow, CI/CD, Snowflake, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877524bbcd4e4f56</t>
+          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Senior Software Engineer (.NET )</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, Data Lake, Apache Airflow, CI/CD, Jenkins, Git, Snowflake, Redshift, Python, SQL</t>
+          <t>LangChain, RAG, Synapse, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
+          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kubernetes / XNAT Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XNAT Works Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Copilot, Glue, Kinesis, Kubernetes, CI/CD, Terraform, Git, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cc83af06965162</t>
+          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>PGIM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Terraform, Git, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Glue, Data Lake, CI/CD, GitHub Actions, Git, PySpark, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5d6144c747c0b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III, Search Relevance</t>
+          <t>Senior Data Engineer - PGIM Technology</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Terraform, Kafka, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, Glue, Data Lake, CI/CD, GitHub Actions, Git, PySpark, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7806dc41ae3cce01</t>
+          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Distinguished Software Engineer (Big Data &amp; AI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>RAG, BigQuery, Dataflow, Git, BigQuery, Kafka, MongoDB, Cassandra, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e446599f1b1f5c54</t>
+          <t>https://www.indeed.com/viewjob?jk=a981ef29c01bf602</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Cortex, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7deb8cb5e2c28</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, BigQuery, CI/CD, Terraform, Git, BigQuery, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a329ecdc04bedbd8</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>Senior IT AI/ML Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e8c12fc04e7cef</t>
+          <t>https://www.indeed.com/viewjob?jk=71f249b5274bf4fb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>Distinguished Software Engineer - ADEM (Backend)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, BigQuery, Dataflow, Kubernetes, Git, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=391d69d149a1d2a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b978835155975ea4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, Kubernetes, Snowflake, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c5fb49d9153d67</t>
+          <t>https://www.indeed.com/viewjob?jk=68a3c77619ac2139</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abdb996f66f95a39</t>
+          <t>https://www.indeed.com/viewjob?jk=89cda98f04e55866</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Data Engineering Specialist - Source AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLOUD5TECH</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MLflow, FastAPI, Snowflake, Databricks, PySpark, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Generative AI, RAG, S3, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9667dae25862c0f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5c6d93ec2ca3a9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr Software Quality Engineer (Exp w/ AI Techniques)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Aspen Technology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bedford, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14376e2563bff55d</t>
+          <t>https://www.indeed.com/viewjob?jk=f74bc4c0820330e5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Data Science Software LLC</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d96ad5f2dd3ad96</t>
+          <t>https://www.indeed.com/viewjob?jk=55da546db249541e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Data Product APIs</t>
+          <t>Senior Automation Engineer(QA)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USA TODAY Co.</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,42 +1196,707 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce51dbe0b401ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=6322e92a61d72261</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Data Product APIs</t>
+          <t>AI Partnerships Solutions Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USA TODAY Co.</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Mistral, Prompt Engineering, GCP Vertex AI, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33b0ea014240acec</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6970ebc1da672a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer, Payments Checkouts - Publishing Platform</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Riot Games</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64dd743e4a8a5177</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI Forward Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tyfone</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b57074d9fc3bd668</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Cortex, Apache Airflow, CI/CD, Git, Snowflake, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9bb8ed9f7e0b915</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Didero</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aca49665b986234d</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Twin Health</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b70067ae55c291ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Account Solution Architect - Financial Services</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CoreWeave, Inc</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, PyTorch, Kubernetes, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d08dba2390f3ac3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Account Solution Architect</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, PyTorch, Kubernetes, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d370edd4d28908c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Area, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>10</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a46068ce48058b8</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52f1c78ef2fc3b0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sr. Java/AWS Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Client Resources, Inc.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8732c30c0b6792f</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Mgr, Cortex Cloud Premium Success</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Cortex, Docker, CI/CD, Jenkins, GitHub Actions, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ee30581c13cbea2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sr Distinguished Software Engineer (DLP Platform Architecture, Scale, and Advanced DLP Detection)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, Kubernetes, Git, Kafka, Cassandra, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a51f51df06fa7d48</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr. Technical Support Engineer, Focused Services, Cortex XSOAR</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, Docker, Kubernetes, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=606682fb55a5222c</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr Site Reliability Engineer (Internet Security Platform)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1a278235c230fa3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Mgr, Customer Success Engineering</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Cortex, Docker, CI/CD, Jenkins, GitHub Actions, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=967d66dc09d7d799</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Associate Engineer, Product Software</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Equinix</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>S3, Docker, GitHub Actions, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b6ad88d61f82d85</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=288bf7dfffd4aa95</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Home Loans Loss Forecasting Analytics, Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d48a35c4876422d</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sr. Software Developer - Platform Engineering Hybrid or Remote</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rocket</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df04eb606c4ae786</t>
         </is>
       </c>
     </row>
